--- a/automatedEval/TFM_Evaluator_Prompt_Package/rubrica MUDPE.xlsx
+++ b/automatedEval/TFM_Evaluator_Prompt_Package/rubrica MUDPE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanjo/Documents/Personal/JJVR/automatizaciones/automatedEval/TFM_Evaluator_Prompt_Package/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF928049-656B-DC45-99A3-3C4217C0A86B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B1C3F0-F90F-6D41-912C-96C6CE896BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21460" yWindow="500" windowWidth="26800" windowHeight="28260" xr2:uid="{22A2D1EC-3F8C-434E-B6E5-5DB57C6AFD5E}"/>
   </bookViews>
@@ -387,10 +387,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="14"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
+        <rFont val="Aptos Display"/>
+        <scheme val="major"/>
       </rPr>
       <t>Estilo formal/académico</t>
     </r>
@@ -403,10 +403,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="14"/>
         <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
+        <rFont val="Aptos Display"/>
+        <scheme val="major"/>
       </rPr>
       <t>· Portada; Resumen; Índice
 · Introducción; Justificación; objetivos
@@ -420,7 +420,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -448,22 +448,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="5">
@@ -603,61 +616,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -994,266 +1008,266 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AA496D9-71D8-0343-844B-38BFC7DE0A68}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46.1640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="42.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.33203125" style="1" customWidth="1"/>
     <col min="6" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="340">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:6" ht="209" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="5"/>
-    </row>
-    <row r="3" spans="1:6" ht="409.6">
-      <c r="A3" s="6" t="s">
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="171" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:6" ht="289">
-      <c r="A4" s="9" t="s">
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" ht="190" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:6" ht="323">
-      <c r="A5" s="10" t="s">
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" ht="190" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:6" ht="409.6">
-      <c r="A6" s="9" t="s">
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="1:6" ht="204">
-      <c r="A7" s="9" t="s">
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" ht="171" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" ht="187">
-      <c r="A8" s="9" t="s">
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" ht="133" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:6" ht="153">
-      <c r="A9" s="9" t="s">
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" ht="95" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6" ht="221">
-      <c r="A10" s="9" t="s">
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" ht="133" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" ht="255">
-      <c r="A11" s="14" t="s">
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" ht="152" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:6" ht="204">
-      <c r="A12" s="14" t="s">
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" ht="133" x14ac:dyDescent="0.2">
+      <c r="A12" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:6" ht="388">
-      <c r="A13" s="14" t="s">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" ht="209" x14ac:dyDescent="0.2">
+      <c r="A13" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:6" ht="273" thickBot="1">
-      <c r="A14" s="15" t="s">
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" ht="153" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="18"/>
+      <c r="F14" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/automatedEval/TFM_Evaluator_Prompt_Package/rubrica MUDPE.xlsx
+++ b/automatedEval/TFM_Evaluator_Prompt_Package/rubrica MUDPE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanjo/Documents/Personal/JJVR/automatizaciones/automatedEval/TFM_Evaluator_Prompt_Package/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B1C3F0-F90F-6D41-912C-96C6CE896BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E2BB7A0-F5A9-4141-B5C3-3D656828B992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21460" yWindow="500" windowWidth="26800" windowHeight="28260" xr2:uid="{22A2D1EC-3F8C-434E-B6E5-5DB57C6AFD5E}"/>
   </bookViews>
@@ -365,18 +365,6 @@
 · Utiliza gestos para enfatizar los contenidos importantes, domina la comunicación no verbal.</t>
   </si>
   <si>
-    <t>Nivel 4</t>
-  </si>
-  <si>
-    <t>Nivel 1</t>
-  </si>
-  <si>
-    <t>Nivel 2</t>
-  </si>
-  <si>
-    <t>Nivel 3</t>
-  </si>
-  <si>
     <t>Criterio</t>
   </si>
   <si>
@@ -415,12 +403,24 @@
 · Limitaciones, principales amenazas y alternativas                                                                                                                                                                                                                                                                                                                           · Referencias bibliográficas</t>
     </r>
   </si>
+  <si>
+    <t>Nivel 1  (0-4)</t>
+  </si>
+  <si>
+    <t>Nivel 2 (5-6)</t>
+  </si>
+  <si>
+    <t>Nivel 3 (7-8)</t>
+  </si>
+  <si>
+    <t>Nivel 4 (9-10)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -478,8 +478,23 @@
       <name val="Aptos Display"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -504,6 +519,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -613,10 +634,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -673,8 +695,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="60% - Énfasis1" xfId="1" builtinId="32"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1020,24 +1045,24 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>63</v>
+      <c r="D1" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="209" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>0</v>
@@ -1055,7 +1080,7 @@
     </row>
     <row r="3" spans="1:6" ht="171" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>4</v>
